--- a/education_forms/044_small_group_instruction_daily_checklist_form--education_forms.xlsx
+++ b/education_forms/044_small_group_instruction_daily_checklist_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Small Group Instruction Daily Checklist Form</t>
+          <t>Small Group Instruction Activity Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,14 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select the category of the activity</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +581,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,30 +604,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_copy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Copy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>student_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Student Progress</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,58 +662,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +726,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>teacher_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Teacher Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>student_progress_notes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Student Progress Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +780,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -815,7 +842,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_copy_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_copy_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -841,40 +868,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
